--- a/frontend/public/templates/aliexpress_warehouse_fulfillment_template.xlsx
+++ b/frontend/public/templates/aliexpress_warehouse_fulfillment_template.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="平台数据" sheetId="1" r:id="rId1"/>
-    <sheet name="字段说明" sheetId="2" r:id="rId2"/>
+    <sheet name="填写示例" sheetId="2" r:id="rId2"/>
+    <sheet name="字段说明" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -13,13 +14,13 @@
   <ns0:cols>
     <ns0:col min="1" max="1" width="16" customWidth="1"/>
     <ns0:col min="2" max="2" width="22" customWidth="1"/>
-    <ns0:col min="3" max="3" width="20" customWidth="1"/>
+    <ns0:col min="3" max="3" width="16" customWidth="1"/>
     <ns0:col min="4" max="4" width="20" customWidth="1"/>
-    <ns0:col min="5" max="5" width="18" customWidth="1"/>
-    <ns0:col min="6" max="6" width="16" customWidth="1"/>
+    <ns0:col min="5" max="5" width="20" customWidth="1"/>
+    <ns0:col min="6" max="6" width="18" customWidth="1"/>
     <ns0:col min="7" max="7" width="16" customWidth="1"/>
-    <ns0:col min="8" max="8" width="18" customWidth="1"/>
-    <ns0:col min="9" max="9" width="16" customWidth="1"/>
+    <ns0:col min="8" max="8" width="16" customWidth="1"/>
+    <ns0:col min="9" max="9" width="18" customWidth="1"/>
     <ns0:col min="10" max="10" width="16" customWidth="1"/>
     <ns0:col min="11" max="11" width="16" customWidth="1"/>
     <ns0:col min="12" max="12" width="16" customWidth="1"/>
@@ -27,8 +28,9 @@
     <ns0:col min="14" max="14" width="16" customWidth="1"/>
     <ns0:col min="15" max="15" width="16" customWidth="1"/>
     <ns0:col min="16" max="16" width="16" customWidth="1"/>
-    <ns0:col min="17" max="17" width="20" customWidth="1"/>
-    <ns0:col min="18" max="18" width="16" customWidth="1"/>
+    <ns0:col min="17" max="17" width="16" customWidth="1"/>
+    <ns0:col min="18" max="18" width="20" customWidth="1"/>
+    <ns0:col min="19" max="19" width="16" customWidth="1"/>
   </ns0:cols>
   <ns0:sheetData>
     <ns0:row r="1">
@@ -44,90 +46,327 @@
       </ns0:c>
       <ns0:c r="C1" t="inlineStr">
         <ns0:is>
+          <ns0:t>单据类型</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" t="inlineStr">
+        <ns0:is>
           <ns0:t>来源平台单据ID</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D1" t="inlineStr">
+      <ns0:c r="E1" t="inlineStr">
         <ns0:is>
           <ns0:t>明细/订单行ID</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E1" t="inlineStr">
+      <ns0:c r="F1" t="inlineStr">
         <ns0:is>
           <ns0:t>平台SKU标识</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F1" t="inlineStr">
+      <ns0:c r="G1" t="inlineStr">
         <ns0:is>
           <ns0:t>平台SKU</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G1" t="inlineStr">
+      <ns0:c r="H1" t="inlineStr">
         <ns0:is>
           <ns0:t>数量</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="H1" t="inlineStr">
+      <ns0:c r="I1" t="inlineStr">
         <ns0:is>
           <ns0:t>订单/备货状态</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I1" t="inlineStr">
+      <ns0:c r="J1" t="inlineStr">
         <ns0:is>
           <ns0:t>组包批次ID</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="J1" t="inlineStr">
+      <ns0:c r="K1" t="inlineStr">
         <ns0:is>
           <ns0:t>包裹/箱号</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="K1" t="inlineStr">
+      <ns0:c r="L1" t="inlineStr">
         <ns0:is>
           <ns0:t>标签编号</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="L1" t="inlineStr">
+      <ns0:c r="M1" t="inlineStr">
         <ns0:is>
           <ns0:t>标签文件名</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="M1" t="inlineStr">
+      <ns0:c r="N1" t="inlineStr">
         <ns0:is>
           <ns0:t>预约编号</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N1" t="inlineStr">
+      <ns0:c r="O1" t="inlineStr">
         <ns0:is>
           <ns0:t>取件开始时间</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="O1" t="inlineStr">
+      <ns0:c r="P1" t="inlineStr">
         <ns0:is>
           <ns0:t>取件结束时间</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P1" t="inlineStr">
+      <ns0:c r="Q1" t="inlineStr">
         <ns0:is>
           <ns0:t>取件时间段</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="Q1" t="inlineStr">
+      <ns0:c r="R1" t="inlineStr">
         <ns0:is>
           <ns0:t>平台数据更新时间</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="R1" t="inlineStr">
+      <ns0:c r="S1" t="inlineStr">
         <ns0:is>
           <ns0:t>目标平台仓</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
+  <ns0:autoFilter ref="A1:S1001"/>
+  <ns0:dataValidations count="2">
+    <ns0:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="固定字段选项" prompt="ALIEXPRESS 为当前支持的平台固定值" errorTitle="请选择列表值" error="请从下拉选项中选择，不要手工修改固定字段。" sqref="A2:A1001">
+      <ns0:formula1>"ALIEXPRESS"</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="固定字段选项" prompt="本模板仅用于仓发入平台仓备货单，固定选择 PLATFORM_WAREHOUSE_STOCKING" errorTitle="请选择列表值" error="请从下拉选项中选择，不要手工修改固定字段。" sqref="C2:C1001">
+      <ns0:formula1>"PLATFORM_WAREHOUSE_STOCKING"</ns0:formula1>
+    </ns0:dataValidation>
+  </ns0:dataValidations>
 </ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="16" customWidth="1"/>
+    <ns0:col min="2" max="2" width="22" customWidth="1"/>
+    <ns0:col min="3" max="3" width="16" customWidth="1"/>
+    <ns0:col min="4" max="4" width="20" customWidth="1"/>
+    <ns0:col min="5" max="5" width="20" customWidth="1"/>
+    <ns0:col min="6" max="6" width="18" customWidth="1"/>
+    <ns0:col min="7" max="7" width="16" customWidth="1"/>
+    <ns0:col min="8" max="8" width="16" customWidth="1"/>
+    <ns0:col min="9" max="9" width="18" customWidth="1"/>
+    <ns0:col min="10" max="10" width="16" customWidth="1"/>
+    <ns0:col min="11" max="11" width="16" customWidth="1"/>
+    <ns0:col min="12" max="12" width="16" customWidth="1"/>
+    <ns0:col min="13" max="13" width="16" customWidth="1"/>
+    <ns0:col min="14" max="14" width="16" customWidth="1"/>
+    <ns0:col min="15" max="15" width="16" customWidth="1"/>
+    <ns0:col min="16" max="16" width="16" customWidth="1"/>
+    <ns0:col min="17" max="17" width="16" customWidth="1"/>
+    <ns0:col min="18" max="18" width="20" customWidth="1"/>
+    <ns0:col min="19" max="19" width="16" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>平台</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>店铺标识/账号标识</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>单据类型</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>来源平台单据ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>明细/订单行ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>平台SKU标识</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>平台SKU</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>数量</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>订单/备货状态</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>组包批次ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>包裹/箱号</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>标签编号</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>标签文件名</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>预约编号</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>取件开始时间</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>取件结束时间</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>取件时间段</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>平台数据更新时间</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>目标平台仓</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ALIEXPRESS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>示例店铺</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PLATFORM_WAREHOUSE_STOCKING</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SAMPLE-STOCK-001</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>STOCK-LINE-001</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PLATFORM-SKU-002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SKU-DEMO-002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>待发货</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BATCH-002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CARTON-001</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LABEL-002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>label-002.pdf</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>APPT-002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-17 09:00:00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-17 12:00:00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>09:00-12:00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-15 10:00:00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>速卖通平台仓示例</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:autoFilter ref="A1:S2"/>
+</ns0:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <ns0:cols>
     <ns0:col min="1" max="1" width="30" customWidth="1"/>
@@ -165,7 +404,7 @@
       </ns0:c>
       <ns0:c r="C2" t="inlineStr">
         <ns0:is>
-          <ns0:t>可选；平台导出包含此字段时建议保留原值</ns0:t>
+          <ns0:t>ALIEXPRESS 为当前支持的平台固定值</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -189,7 +428,7 @@
     <ns0:row r="4">
       <ns0:c r="A4" t="inlineStr">
         <ns0:is>
-          <ns0:t>来源平台单据ID</ns0:t>
+          <ns0:t>单据类型</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B4" t="inlineStr">
@@ -199,31 +438,31 @@
       </ns0:c>
       <ns0:c r="C4" t="inlineStr">
         <ns0:is>
-          <ns0:t>速卖通仓发入平台仓备货单 ID</ns0:t>
+          <ns0:t>固定填写 PLATFORM_WAREHOUSE_STOCKING；本模板仅用于仓发入平台仓备货单</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="5">
       <ns0:c r="A5" t="inlineStr">
         <ns0:is>
-          <ns0:t>明细/订单行ID</ns0:t>
+          <ns0:t>来源平台单据ID</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>否</ns0:t>
+          <ns0:t>是</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5" t="inlineStr">
         <ns0:is>
-          <ns0:t>可选；平台导出包含此字段时建议保留原值</ns0:t>
+          <ns0:t>速卖通仓发入平台仓备货单 ID</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
       <ns0:c r="A6" t="inlineStr">
         <ns0:is>
-          <ns0:t>平台SKU标识</ns0:t>
+          <ns0:t>明细/订单行ID</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
@@ -240,24 +479,24 @@
     <ns0:row r="7">
       <ns0:c r="A7" t="inlineStr">
         <ns0:is>
-          <ns0:t>平台SKU</ns0:t>
+          <ns0:t>平台SKU标识</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>是</ns0:t>
+          <ns0:t>否</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C7" t="inlineStr">
         <ns0:is>
-          <ns0:t>用于匹配店铺 SKU 映射，必须与平台导出值一致</ns0:t>
+          <ns0:t>可选；平台导出包含此字段时建议保留原值</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
       <ns0:c r="A8" t="inlineStr">
         <ns0:is>
-          <ns0:t>数量</ns0:t>
+          <ns0:t>平台SKU</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
@@ -267,31 +506,31 @@
       </ns0:c>
       <ns0:c r="C8" t="inlineStr">
         <ns0:is>
-          <ns0:t>备货明细数量，必须大于 0</ns0:t>
+          <ns0:t>用于匹配店铺 SKU 映射，必须与平台导出值一致</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="9">
       <ns0:c r="A9" t="inlineStr">
         <ns0:is>
-          <ns0:t>订单/备货状态</ns0:t>
+          <ns0:t>数量</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>否</ns0:t>
+          <ns0:t>是</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9" t="inlineStr">
         <ns0:is>
-          <ns0:t>可选；平台导出包含此字段时建议保留原值</ns0:t>
+          <ns0:t>备货明细数量，必须大于 0</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="10">
       <ns0:c r="A10" t="inlineStr">
         <ns0:is>
-          <ns0:t>组包批次ID</ns0:t>
+          <ns0:t>订单/备货状态</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
@@ -308,7 +547,7 @@
     <ns0:row r="11">
       <ns0:c r="A11" t="inlineStr">
         <ns0:is>
-          <ns0:t>包裹/箱号</ns0:t>
+          <ns0:t>组包批次ID</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B11" t="inlineStr">
@@ -325,7 +564,7 @@
     <ns0:row r="12">
       <ns0:c r="A12" t="inlineStr">
         <ns0:is>
-          <ns0:t>标签编号</ns0:t>
+          <ns0:t>包裹/箱号</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B12" t="inlineStr">
@@ -342,7 +581,7 @@
     <ns0:row r="13">
       <ns0:c r="A13" t="inlineStr">
         <ns0:is>
-          <ns0:t>标签文件名</ns0:t>
+          <ns0:t>标签编号</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B13" t="inlineStr">
@@ -359,7 +598,7 @@
     <ns0:row r="14">
       <ns0:c r="A14" t="inlineStr">
         <ns0:is>
-          <ns0:t>预约编号</ns0:t>
+          <ns0:t>标签文件名</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B14" t="inlineStr">
@@ -376,7 +615,7 @@
     <ns0:row r="15">
       <ns0:c r="A15" t="inlineStr">
         <ns0:is>
-          <ns0:t>取件开始时间</ns0:t>
+          <ns0:t>预约编号</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B15" t="inlineStr">
@@ -393,7 +632,7 @@
     <ns0:row r="16">
       <ns0:c r="A16" t="inlineStr">
         <ns0:is>
-          <ns0:t>取件结束时间</ns0:t>
+          <ns0:t>取件开始时间</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B16" t="inlineStr">
@@ -410,7 +649,7 @@
     <ns0:row r="17">
       <ns0:c r="A17" t="inlineStr">
         <ns0:is>
-          <ns0:t>取件时间段</ns0:t>
+          <ns0:t>取件结束时间</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B17" t="inlineStr">
@@ -427,7 +666,7 @@
     <ns0:row r="18">
       <ns0:c r="A18" t="inlineStr">
         <ns0:is>
-          <ns0:t>平台数据更新时间</ns0:t>
+          <ns0:t>取件时间段</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B18" t="inlineStr">
@@ -444,20 +683,38 @@
     <ns0:row r="19">
       <ns0:c r="A19" t="inlineStr">
         <ns0:is>
+          <ns0:t>平台数据更新时间</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>否</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>可选；平台导出包含此字段时建议保留原值</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" t="inlineStr">
+        <ns0:is>
           <ns0:t>目标平台仓</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="B19" t="inlineStr">
+      <ns0:c r="B20" t="inlineStr">
         <ns0:is>
           <ns0:t>是</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C19" t="inlineStr">
+      <ns0:c r="C20" t="inlineStr">
         <ns0:is>
           <ns0:t>备货单的目标平台仓名称或代码</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
+  <ns0:autoFilter ref="A1:C20"/>
 </ns0:worksheet>
 </file>